--- a/templates/Статистика за год на данный момент.xlsx
+++ b/templates/Статистика за год на данный момент.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravil\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Public\bnk-diplom-abiturient-system\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80634E4C-5F0D-4436-991A-0B43F1C27D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C4986D-4E61-4179-B9C2-E27865016BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="540" windowWidth="29040" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -150,17 +150,8 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -169,10 +160,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,7 +458,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="2" max="2" width="52.5703125" customWidth="1"/>
     <col min="3" max="3" width="11.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.140625" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
@@ -466,72 +466,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="9"/>
+      <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8" t="s">
+      <c r="A4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="5" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/templates/Статистика за год на данный момент.xlsx
+++ b/templates/Статистика за год на данный момент.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Public\bnk-diplom-abiturient-system\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C4986D-4E61-4179-B9C2-E27865016BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1452222-239D-4705-8CC8-A30339375A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="540" windowWidth="29040" windowHeight="15780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
-    <t xml:space="preserve">Количество заявлений, поданных в ГАПОУ «Бугурусланский нефтяной колледж » г. Бугуруслана </t>
-  </si>
-  <si>
     <t>Код специальности, профессии</t>
   </si>
   <si>
@@ -49,6 +46,9 @@
   </si>
   <si>
     <t>на "25" июня 2025 года</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Количество заявлений, поданных в ГАПОУ «Бугурусланский нефтяной колледж» г. Бугуруслана </t>
   </si>
 </sst>
 </file>
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -159,12 +159,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -172,7 +166,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,56 +462,56 @@
     <col min="6" max="6" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="6"/>
+    <row r="1" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+    <row r="2" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
     </row>
     <row r="3" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="7"/>
+      <c r="E3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="9"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>6</v>
-      </c>
       <c r="E4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -538,7 +535,7 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
